--- a/Backend/tablas_generadas/tablita.xlsx
+++ b/Backend/tablas_generadas/tablita.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,26 +436,25 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Hotdog King (Steam)</t>
+          <t>Google Classroom</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Hot Dog Clicker Idle (Google Play)</t>
+          <t>Moodle</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Hotdog Clicker (itch.io)</t>
+          <t>Canvas LMS</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Cookie Clicker (Oficial)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr">
+          <t>ORT Argentina - Campus Virtual</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>conclusion</t>
         </is>
@@ -469,28 +468,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Texto claro y legible. El sitio emplea fuentes estándar de Steam, asegurando una buena legibilidad en la plataforma de distribución digital para todos los jugadores.</t>
+          <t>Claridad tipográfica. Utiliza fuentes sans-serif nítidas y tamaños bien jerarquizados, asegurando una óptima legibilidad en cualquier dispositivo digital.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fuentes sencillas y directas. Utiliza tipografías básicas de Android, favoreciendo una comprensión rápida y sin esfuerzo en pantallas de dispositivos móviles de diversos tamaños.</t>
+          <t>Presentación funcional de texto. Emplea tipografías estándares que facilitan la lectura, con un espaciado adecuado para la fluidez y comprensión del contenido.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estilo retro evidente. La tipografía complementa una estética pixelada, aunque en ocasiones el contraste puede dificultar una lectura fluida durante periodos prolongados.</t>
+          <t>Diseño tipográfico moderno. Combina fuentes limpias y tamaños variados con un contraste excelente, promoviendo una experiencia de lectura muy agradable y eficiente.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fuentes elegantes y temáticas. La tipografía escogida realza la atmósfera del juego, manteniendo una excelente legibilidad a pesar de su estilo visual distintivo y único.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Considerar una fuente más moderna y nítida para los elementos principales, mejorando la claridad en pantallas de alta resolución sin sacrificar el encanto.</t>
+          <t>Fuentes básicas, legibles. La interfaz utiliza tipografías estándar que brindan claridad en los textos, aplicando jerarquía visual mediante distintos tamaños y pesos.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Considerar el uso de una gama tipográfica más diversa o estilos que permitan destacar secciones clave, mejorando la jerarquía y el atractivo visual general del texto.</t>
         </is>
       </c>
     </row>
@@ -502,28 +500,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Colores vibrantes y atractivos. Predominan tonos cálidos y llamativos, reflejando la temática de comida rápida y la diversión inherente a la experiencia del juego.</t>
+          <t>Paleta de colores sencilla. Predominan los tonos blancos y grises, con acentos de azul para elementos interactivos, manteniendo una identidad visual limpia y coherente.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Diseño funcional y colorido. Los colores brillantes se usan para distinguir elementos interactivos, logrando una interfaz intuitiva y muy amigable para usuarios móviles.</t>
+          <t>Esquema de color configurable. Los temas permiten la adaptación de la paleta, aunque la base es funcional con azules y blancos institucionales muy reconocibles.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Paleta vintage y limitada. Emplea una combinación de colores que evoca los juegos de 8 bits, creando una identidad visual coherente y profundamente nostálgica para el jugador.</t>
+          <t>Uso estratégico del color. Colores corporativos bien integrados guían eficazmente la atención del usuario, ofreciendo una experiencia visual moderna y cohesiva.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Esquema cromático coherente. Predominan los tonos tierra y azules oscuros, creando una atmósfera misteriosa que se alinea perfectamente con la estética general del juego.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Reforzar la paleta con acentos más vivos para elementos clave y promociones, atrayendo visualmente a nuevos usuarios mientras se mantiene la identidad existente.</t>
+          <t>Colores institucionales predominantes. El azul oscuro y el blanco son la base de la identidad visual, con toques de azul cielo en elementos interactivos y gráficos.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Asegurar la consistencia exacta de los tonos azules en todos los elementos y explorar la inclusión de una paleta secundaria sutil para diferenciar contenidos sin perder la marca.</t>
         </is>
       </c>
     </row>
@@ -535,28 +532,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gráficos detallados y apetitosos. Presenta imágenes de alta calidad de panchos y elementos culinarios, incitando al usuario a probar la divertida experiencia del producto digital.</t>
+          <t>Iconografía minimalista y funcional. Emplea íconos claros y concisos que enriquecen la comprensión de las acciones y facilitan una navegación directa e intuitiva.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iconos sencillos y animados. Los elementos visuales son directos y refuerzan la jugabilidad, optimizados para una experiencia móvil fluida y muy amigable para todos.</t>
+          <t>Elementos visuales adaptables. Incluye iconos, ilustraciones sencillas y fotografías, ajustables por tema, que contextualizan la información de manera eficaz.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estilo pixel art nostálgico. Destaca por sus gráficos retro, ofreciendo una experiencia visual única que apela directamente a los aficionados a los videojuegos clásicos con encanto.</t>
+          <t>Imágenes y gráficos atractivos. Predominan fotografías de alta calidad e iconografía moderna que enriquecen la interfaz, optimizando la experiencia visual del usuario.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Iconos icónicos y detallados. Los elementos visuales son reconocibles al instante y contribuyen significativamente a la inmersión del jugador, manteniendo una calidad constante.</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Actualizar ciertos íconos y animaciones para que se sientan más modernos y dinámicos, manteniendo la estética original pero mejorando la fluidez visual general.</t>
+          <t>Integración de imágenes y logos. Se observan fotografías de estudiantes y el logotipo institucional claramente, junto a un banner principal con información destacada.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Incorporar más iconografía relevante para guiar al usuario y mejorar la calidad y el estilo de las imágenes para hacer el contenido más dinámico y visualmente atractivo.</t>
         </is>
       </c>
     </row>
@@ -568,28 +564,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Flujo de usuario estándar. La navegación sigue los patrones habituales de Steam, facilitando a los jugadores encontrar información crucial y realizar sus compras de manera eficiente.</t>
+          <t>Navegación intuitiva y directa. Los menús están simplificados y las rutas son claras, facilitando el acceso rápido a las funciones esenciales para todos los usuarios.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Interfaz táctil intuitiva. La navegación está optimizada para gestos, permitiendo a los usuarios interactuar con gran facilidad desde sus dispositivos móviles en todo momento.</t>
+          <t>Estructura de navegación flexible. Menús desplegables y bloques laterales permiten personalizar la organización del contenido, optimizando la experiencia de cada usuario.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estructura directa y básica. La navegación es mínima y se centra en el juego, lo que simplifica el acceso para los usuarios que buscan una experiencia clicker rápida y sin complicaciones.</t>
+          <t>Experiencia de usuario refinada. La navegación es fluida, con llamadas a la acción explícitas y una arquitectura de información lógicamente estructurada y predecible.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Menús claros y accesibles. La interfaz de usuario es sencilla y eficiente, permitiendo a los jugadores acceder rápidamente a las opciones y estadísticas importantes del juego.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Mejorar la organización de algunos paneles, quizás agrupando opciones similares para reducir la sobrecarga cognitiva y agilizar la toma de decisiones del jugador.</t>
+          <t>Menú superior con submenús. La navegación principal es visible y organizada por categorías claras, ofreciendo una estructura de contenido lógica.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Añadir un campo de búsqueda visible en la cabecera para facilitar la localización de contenido, y considerar la implementación de migas de pan para mejorar la orientación dentro del sitio.</t>
         </is>
       </c>
     </row>
@@ -601,28 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Contenido bien segmentado. La página de Steam organiza la información en secciones lógicas, guiando al usuario desde la descripción detallada hasta las valiosas reseñas de otros jugadores.</t>
+          <t>Contenido organizado modularmente. La información se presenta en secciones bien definidas, lo que optimiza la escaneabilidad y la comprensión rápida de las tareas.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Diseño compacto y eficiente. La estructura se adapta muy bien a pantallas pequeñas, presentando la información esencial sin saturar al usuario móvil con datos innecesarios.</t>
+          <t>Diseño de página adaptable. La disposición de los elementos es personalizable, permitiendo a los administradores ajustar la jerarquía visual de los contenidos según las necesidades.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Disposición concisa y enfocada. La organización de la página es minimalist, priorizando el acceso inmediato al juego y a la información básica vital del desarrollador fácilmente.</t>
+          <t>Distribución lógica de contenido. Utiliza un grid moderno y una jerarquía visual clara para guiar la atención del usuario, facilitando la asimilación de la información clave.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Layout clásico y funcional. La estructura principal del juego divide la pantalla en áreas distintas para la producción, tienda y estadísticas, facilitando el seguimiento constante.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Revisar la jerarquía de la información en ciertas secciones secundarias, asegurando que los datos más importantes sean prominentes y fáciles de localizar para los jugadores nuevos.</t>
+          <t>Distribución en columnas y bloques. El contenido principal se organiza en una cuadrícula sencilla, complementada con bloques laterales para noticias y banners informativos.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Optimizar la distribución de los bloques para evitar la densidad visual en ciertas áreas y potenciar la legibilidad mediante un uso más estratégico del espacio en blanco.</t>
         </is>
       </c>
     </row>
@@ -634,28 +628,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cumplimiento de estándares Steam. La plataforma ofrece opciones de accesibilidad inherentes, beneficiando a una audiencia amplia con diversas necesidades y preferencias de uso.</t>
+          <t>Enfoque en accesibilidad. Presenta un buen contraste de texto, navegación por teclado y etiquetas ARIA, facilitando el uso para todos los usuarios, incluyendo con discapacidad.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Funciones de accesibilidad móvil. El juego se beneficia de características del sistema operativo Android, aunque la propia aplicación podría mejorar sus configuraciones internas.</t>
+          <t>Compatibilidad con estándares. Permite configurar temas accesibles y cumple con las pautas WCAG, garantizando la usabilidad para personas con distintas necesidades.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Opciones básicas disponibles. El sitio ofrece una experiencia generalmente accesible, pero con margen para mejorar el contraste o tamaño de texto para usuarios específicos.</t>
+          <t>Diseño inclusivo. Proporciona altos contrastes, una navegación consistente y soporte para tecnologías de asistencia, mejorando la experiencia para usuarios diversos.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Traducciones extensas presentes. El juego ofrece un menú para cambiar de idioma, lo cual mejora notablemente la accesibilidad lingüística para una audiencia global muy diversa.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Añadir opciones de personalización como contraste de color o tamaño de fuente, permitiendo a más usuarios disfrutar plenamente del juego independientemente de sus capacidades visuales.</t>
+          <t>Contraste general adecuado. Los textos principales tienen buen contraste con el fondo blanco, lo que contribuye a la legibilidad visual para la mayoría de usuarios.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Implementar etiquetas 'alt' descriptivas en todas las imágenes y asegurar un foco visible claro en elementos interactivos para usuarios que navegan con teclado.</t>
         </is>
       </c>
     </row>
@@ -667,28 +660,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Funciones robustas de juego. La aplicación ofrece una experiencia fluida con mecánicas clicker complejas, entregando todo lo prometido en su descripción oficial sin fallos.</t>
+          <t>Conjunto de herramientas robustas. Ofrece gestión de cursos, asignaciones, foros y evaluaciones, integrándose eficientemente con otras aplicaciones de productividad.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mecánicas de juego sólidas. El juego cumple su propósito de clicker inactivo, permitiendo a los jugadores progresar con interacciones simples y recompensas inmediatas.</t>
+          <t>Plataforma altamente funcional. Proporciona módulos extensibles para calificaciones, foros, wikis y permite la integración con una amplia gama de plugins educativos.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Operatividad sencilla y directa. El juego se carga rápidamente y sus funcionalidades básicas están operativas, brindando una experiencia de juego instantánea y sin complicaciones.</t>
+          <t>Funcionalidades avanzadas. Incluye analíticas de aprendizaje, herramientas de colaboración, gestión de contenido y un sistema de seguimiento completo para el progreso estudiantil.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Juego estable y completo. La aplicación funciona impecablemente, procesando clics y mejoras de manera eficiente, proporcionando una experiencia de juego ininterrumpida y adictiva.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Investigar y corregir posibles micro-errores en actualizaciones, asegurando que todas las nuevas características se integren sin afectar la estabilidad general ni el rendimiento.</t>
+          <t>Acceso a portal de usuario. Un icono de perfil visible sugiere inicio de sesión, paneles personalizados y acceso a contenidos educativos básicos para los alumnos.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Desarrollar una sección clara de 'Mis Cursos' o 'Mi Espacio' para usuarios autenticados, y detallar las posibles integraciones clave con herramientas externas relevantes.</t>
         </is>
       </c>
     </row>
@@ -700,28 +692,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alto grado de interacción. El juego fomenta la participación constante del jugador a través de clics, mejoras y decisiones estratégicas para optimizar la valiosa producción.</t>
+          <t>Interacciones fluidas y directas. Los elementos interactivos como botones y enlaces ofrecen un feedback visual claro al ser seleccionados o enfocados.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Interacción constante y progresiva. Los usuarios participan mediante toques continuos y decisiones sobre mejoras, manteniendo un compromiso activo y muy gratificante.</t>
+          <t>Capacidades interactivas extensibles. Soporta diversas actividades con retroalimentación inmediata, como cuestionarios y encuestas, fomentando la participación activa.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Interactividad básica y constante. La mecánica central de clics es el eje principal, ofreciendo una experiencia directa y gratificante para los amantes del género clicker.</t>
+          <t>Microinteracciones bien diseñadas. Los estados hover y active son sutiles y responsivos, mejorando la experiencia del usuario sin generar distracciones innecesarias.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Engagement adictivo garantizado. La interacción principal es el clic, complementada con mejoras estratégicas que mantienen al jugador enganchado por horas de diversión.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Introducir minijuegos o eventos temporales con mecánicas de interacción diferentes, añadiendo variedad y frescura a la experiencia de juego principal para mantener el interés a largo plazo.</t>
+          <t>Elementos interactivos básicos. Se observan flechas de navegación en un carrusel y enlaces de texto que presumiblemente tienen estados hover simples al interactuar.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Enriquecer las microinteracciones en botones y enlaces, añadiendo sutiles animaciones o cambios de color para mejorar el feedback visual al usuario.</t>
         </is>
       </c>
     </row>
@@ -733,74 +724,75 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optimizado para la plataforma. El juego utiliza palabras clave relevantes dentro de Steam, mejorando su visibilidad y alcanzando a una audiencia específica de jugadores potenciales.</t>
+          <t>Optimizado para buscadores. Utiliza títulos y meta descripciones relevantes, una estructura de encabezados lógica y datos estructurados para mayor visibilidad.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Metadatos específicos para tienda. La descripción y las etiquetas están bien optimizadas para búsquedas en la Play Store, facilitando su descubrimiento móvil fácilmente.</t>
+          <t>Facilidades de SEO integradas. Permite la personalización de URLs, metadatos y facilita la indexación de contenidos educativos para un mayor alcance orgánico.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Presencia básica online. El juego se apoya principalmente en la plataforma itch.io para su visibilidad, con oportunidades para expandir su valioso alcance SEO externo.</t>
+          <t>Estrategia SEO proactiva. Implementa una jerarquía clara de encabezados, títulos optimizados y una estructura URL amigable para buscadores, mejorando su posicionamiento.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dominio reconocido y autoridad. El sitio se beneficia de años de existencia y enlaces externos, posicionándose fuertemente en búsquedas relacionadas con juegos clicker.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Implementar un blog o sección de noticias con contenido regular y optimizado, usando palabras clave relevantes para atraer tráfico orgánico y mantener a la comunidad informada.</t>
+          <t>URL legible y título de página. La dirección web es descriptiva y el título del navegador incluye la marca y 'Campus Virtual', lo cual es un buen punto de partida.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Añadir una meta descripción atractiva y descriptiva para la página principal, y asegurar el uso correcto de las etiquetas H1 y otros encabezados en el contenido visible.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mobile Experience</t>
+          <t>Performance and Loading Times</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Adaptabilidad en Steam Deck. Aunque no es móvil nativo, se beneficia de la compatibilidad con Steam Deck, ofreciendo una experiencia portátil de calidad superior.</t>
+          <t>Rendimiento veloz y eficiente. Optimizado para cargas rápidas, utiliza técnicas como lazy-load, garantizando una experiencia de usuario ágil y sin esperas excesivas.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Optimizado para smartphones. El diseño responsivo y los controles táctiles garantizan una experiencia fluida y muy agradable en cualquier dispositivo móvil.</t>
+          <t>Optimización de velocidad. El rendimiento es generalmente bueno, con opciones de caché para acelerar la entrega de contenido a los usuarios en diversas ubicaciones.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Experiencia web responsiva. Aunque no es una aplicación nativa, el juego se adapta razonablemente bien a diferentes tamaños de pantalla en navegadores móviles.</t>
+          <t>Experiencia de carga fluida. Se enfoca en la eficiencia, minimizando el peso de la página y priorizando la visibilidad rápida del contenido principal y esencial.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Versión móvil dedicada. Aunque existen versiones en tiendas de apps, la experiencia web actual podría beneficiarse de un diseño más adaptable a pantallas pequeñas.</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Desarrollar una interfaz más responsiva para la versión web, asegurando que todos los elementos se escalen y reorganicen correctamente en dispositivos móviles para una jugabilidad óptima.</t>
+          <t>Percepción de carga aceptable. Visualmente, el contenido parece cargar de forma razonable, sin grandes elementos pesados que sugieran una lentitud excesiva en la conexión.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Evaluar el peso de las imágenes principales y aplicar técnicas de lazy-load si es necesario, para asegurar tiempos de carga óptimos, especialmente en conexiones lentas o móviles.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Final Conclusion</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>La aplicación sobresale por su jugabilidad adictiva y su estética coherente. Podría mejorar su atractivo visual mediante la actualización de algunos activos gráficos, expandir la interactividad con nuevos modos de juego y optimizar la versión web para dispositivos móviles.</t>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>El sitio exhibe una base funcional sólida con una identidad de marca clara y navegación eficiente. Para una mejora integral, se recomienda enriquecer los elementos visuales con más iconografía, optimizar la usabilidad incluyendo un buscador y migas de pan, mejorar la interactividad con feedback más pronunciado, y fortalecer el rendimiento web junto a los metadatos SEO. Estas acciones potenciarán la experiencia del usuario y la visibilidad del campus virtual.</t>
         </is>
       </c>
     </row>
